--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.97506373225205</v>
+        <v>4.383447856490958</v>
       </c>
       <c r="D2" t="n">
-        <v>26.1102757213439</v>
+        <v>4.242919804718383</v>
       </c>
       <c r="E2" t="n">
-        <v>6.182252108128766</v>
+        <v>1.004615967570925</v>
       </c>
       <c r="F2" t="n">
-        <v>4.942430472308911</v>
+        <v>0.8031449517501978</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.56234700942274</v>
+        <v>5.291381389031196</v>
       </c>
       <c r="D3" t="n">
-        <v>20.92609028797733</v>
+        <v>3.400489671796316</v>
       </c>
       <c r="E3" t="n">
-        <v>6.182252108128766</v>
+        <v>1.004615967570925</v>
       </c>
       <c r="F3" t="n">
-        <v>4.942430472308911</v>
+        <v>0.8031449517501978</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.99037449058542</v>
+        <v>4.87343585472013</v>
       </c>
       <c r="D4" t="n">
-        <v>29.09047604158526</v>
+        <v>4.727202356757605</v>
       </c>
       <c r="E4" t="n">
-        <v>6.182252108128766</v>
+        <v>1.004615967570925</v>
       </c>
       <c r="F4" t="n">
-        <v>4.942430472308911</v>
+        <v>0.8031449517501978</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.31537120988827</v>
+        <v>2.651247821606844</v>
       </c>
       <c r="D5" t="n">
-        <v>16.16892899663281</v>
+        <v>2.627450961952832</v>
       </c>
       <c r="E5" t="n">
-        <v>6.182252108128766</v>
+        <v>1.004615967570925</v>
       </c>
       <c r="F5" t="n">
-        <v>4.942430472308911</v>
+        <v>0.8031449517501978</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
